--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -100,172 +100,130 @@
     <x:t>BEAN, MELISSA LUBURICH</x:t>
   </x:si>
   <x:si>
+    <x:t>H6IL09228</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BISS, DANIEL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL09194</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FINE, LAURA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6KY04171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GALLREIN, ED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>04</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
     <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
-    <x:t>H4MO01134</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BELL, WESLEY</x:t>
+    <x:t>H6CA14163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HERNANDEZ, MELISSA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8NJ07223</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MALINOWSKI, TOM</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NJ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2KY04121</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00935049</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6IL02355</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6AK00276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PELTOLA, MARY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AK</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NH01321</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SHAHEEN, STEFANY</x:t>
   </x:si>
   <x:si>
     <x:t>01</x:t>
   </x:si>
   <x:si>
-    <x:t>MO</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09228</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BISS, DANIEL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8MO01143</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BUSH, CORI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00418</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EL-SAYED, ABDUL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MI</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL09194</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FINE, LAURA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6KY04171</x:t>
-  </x:si>
-  <x:si>
-    <x:t>GALLREIN, ED</x:t>
-  </x:si>
-  <x:si>
-    <x:t>04</x:t>
-  </x:si>
-  <x:si>
-    <x:t>KY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6CA14163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H8NJ07223</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MALINOWSKI, TOM</x:t>
-  </x:si>
-  <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NJ</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H2KY04121</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MASSIE, THOMAS H.</x:t>
+    <x:t>NH</x:t>
   </x:si>
   <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
     <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00392</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MCMORROW, MALLORY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00935049</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AFFORDABLE CHICAGO NOW! (ACN)</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6IL02355</x:t>
-  </x:si>
-  <x:si>
-    <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6AK00276</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H6NH01321</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
-  </x:si>
-  <x:si>
-    <x:t>S6MI00426</x:t>
-  </x:si>
-  <x:si>
-    <x:t>STEVENS, HALEY</x:t>
   </x:si>
   <x:si>
     <x:t>H0CA15213</x:t>
@@ -345,8 +303,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
-  <x:autoFilter ref="A1:J22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
+  <x:autoFilter ref="A1:J16"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -651,7 +609,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J22"/>
+  <x:dimension ref="A1:J16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -829,34 +787,34 @@
     </x:row>
     <x:row r="6" spans="1:10">
       <x:c r="A6" s="1" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="B6" s="1" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="C6" s="1" t="s">
         <x:v>28</x:v>
       </x:c>
-      <x:c r="B6" s="1" t="s">
+      <x:c r="D6" s="1" t="s">
         <x:v>29</x:v>
       </x:c>
-      <x:c r="C6" s="1" t="s">
-        <x:v>30</x:v>
-      </x:c>
-      <x:c r="D6" s="1" t="s">
-        <x:v>31</x:v>
-      </x:c>
       <x:c r="E6" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F6" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G6" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H6" s="1">
-        <x:v>685625</x:v>
+        <x:v>1426379</x:v>
       </x:c>
       <x:c r="I6" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J6" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="7" spans="1:10">
@@ -867,10 +825,10 @@
         <x:v>25</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
@@ -882,167 +840,167 @@
         <x:v>16</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>1426379</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="D8" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="E8" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F8" s="1" t="s">
         <x:v>36</x:v>
       </x:c>
-      <x:c r="D8" s="1" t="s">
+      <x:c r="G8" s="1" t="s">
         <x:v>37</x:v>
       </x:c>
-      <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F8" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G8" s="1" t="s">
-        <x:v>33</x:v>
-      </x:c>
       <x:c r="H8" s="1">
-        <x:v>2457788</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J8" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>17793547</x:v>
+        <x:v>825294</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>4383749</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>3515616</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>825294</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1053,92 +1011,92 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>28</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>29</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>2326917</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>3232621</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>50000</x:v>
+        <x:v>108000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1149,225 +1107,33 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>4379246</x:v>
+        <x:v>1642139</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:10">
-      <x:c r="A17" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="H17" s="1">
-        <x:v>253750</x:v>
-      </x:c>
-      <x:c r="I17" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:10">
-      <x:c r="A18" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="B18" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="C18" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>32</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="H18" s="1">
-        <x:v>1137283</x:v>
-      </x:c>
-      <x:c r="I18" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J18" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:10">
-      <x:c r="A19" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="B19" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
-      <x:c r="C19" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D19" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H19" s="1">
-        <x:v>31115</x:v>
-      </x:c>
-      <x:c r="I19" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J19" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:10">
-      <x:c r="A20" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B20" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C20" s="1" t="s">
-        <x:v>82</x:v>
-      </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>42</x:v>
-      </x:c>
-      <x:c r="H20" s="1">
-        <x:v>2061287</x:v>
-      </x:c>
-      <x:c r="I20" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:10">
-      <x:c r="A21" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="B21" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="C21" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H21" s="1">
-        <x:v>108000</x:v>
-      </x:c>
-      <x:c r="I21" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J21" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:10">
-      <x:c r="A22" s="1" t="s">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="B22" s="1" t="s">
-        <x:v>29</x:v>
-      </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>85</x:v>
-      </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="H22" s="1">
-        <x:v>1642139</x:v>
-      </x:c>
-      <x:c r="I22" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -185,6 +185,18 @@
   </x:si>
   <x:si>
     <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0FL13158</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PAULINA LUNA, ANNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
   </x:si>
   <x:si>
     <x:t>S6AK00276</x:t>
@@ -303,8 +315,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
-  <x:autoFilter ref="A1:J16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
+  <x:autoFilter ref="A1:J17"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -609,7 +621,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J16"/>
+  <x:dimension ref="A1:J17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1023,48 +1035,48 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="F13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>253750</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="F14" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>566488</x:v>
+        <x:v>253750</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1075,28 +1087,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="D15" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>108000</x:v>
+        <x:v>566488</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1107,33 +1119,65 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
         <x:v>43</x:v>
       </x:c>
       <x:c r="H16" s="1">
+        <x:v>108000</x:v>
+      </x:c>
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
         <x:v>1642139</x:v>
       </x:c>
-      <x:c r="I16" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -136,18 +136,6 @@
     <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
-    <x:t>H6CA14163</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HERNANDEZ, MELISSA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
-  </x:si>
-  <x:si>
     <x:t>H8NJ07223</x:t>
   </x:si>
   <x:si>
@@ -199,21 +187,6 @@
     <x:t>FL</x:t>
   </x:si>
   <x:si>
-    <x:t>S6AK00276</x:t>
-  </x:si>
-  <x:si>
-    <x:t>PELTOLA, MARY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>Senate</x:t>
-  </x:si>
-  <x:si>
-    <x:t>00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AK</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -230,21 +203,6 @@
   </x:si>
   <x:si>
     <x:t>NH</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00815753</x:t>
-  </x:si>
-  <x:si>
-    <x:t>J STREET ACTION FUND</x:t>
-  </x:si>
-  <x:si>
-    <x:t>H0CA15213</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WAHAB, AISHA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -315,8 +273,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
-  <x:autoFilter ref="A1:J17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J13" totalsRowShown="0">
+  <x:autoFilter ref="A1:J13"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -621,7 +579,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J17"/>
+  <x:dimension ref="A1:J13"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -916,21 +874,21 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>825294</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
         <x:v>44</x:v>
@@ -942,13 +900,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>2326917</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -959,10 +917,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>48</x:v>
@@ -974,211 +932,83 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>3232621</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>4379246</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>299290</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:10">
-      <x:c r="A14" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="B14" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="H14" s="1">
-        <x:v>253750</x:v>
-      </x:c>
-      <x:c r="I14" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="s">
         <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:10">
-      <x:c r="A15" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
-      <x:c r="B15" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="H15" s="1">
-        <x:v>566488</x:v>
-      </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:10">
-      <x:c r="A16" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="B16" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H16" s="1">
-        <x:v>108000</x:v>
-      </x:c>
-      <x:c r="I16" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:10">
-      <x:c r="A17" s="1" t="s">
-        <x:v>38</x:v>
-      </x:c>
-      <x:c r="B17" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="C17" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
-      <x:c r="H17" s="1">
-        <x:v>1642139</x:v>
-      </x:c>
-      <x:c r="I17" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -130,6 +130,24 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0NY02267</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LIPETRI, MIKE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>03</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00799031</x:t>
   </x:si>
   <x:si>
@@ -185,12 +203,6 @@
   </x:si>
   <x:si>
     <x:t>FL</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
   </x:si>
   <x:si>
     <x:t>H6NH01321</x:t>
@@ -273,8 +285,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J13" totalsRowShown="0">
-  <x:autoFilter ref="A1:J13"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J14" totalsRowShown="0">
+  <x:autoFilter ref="A1:J14"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -579,7 +591,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J13"/>
+  <x:dimension ref="A1:J14"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -874,7 +886,7 @@
         <x:v>43</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>2326917</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -885,28 +897,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -917,66 +929,66 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
@@ -1002,12 +1014,44 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="H13" s="1">
+        <x:v>299290</x:v>
+      </x:c>
+      <x:c r="I13" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J13" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:10">
+      <x:c r="A14" s="1" t="s">
+        <x:v>38</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="H14" s="1">
         <x:v>159276</x:v>
       </x:c>
-      <x:c r="I13" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J13" s="1" t="s">
+      <x:c r="I14" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -106,6 +106,21 @@
     <x:t>BISS, DANIEL</x:t>
   </x:si>
   <x:si>
+    <x:t>C00863472</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDW ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4PA08124</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRESNAHAN, ROB</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
@@ -185,12 +200,6 @@
   </x:si>
   <x:si>
     <x:t>02</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00863472</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDW ACTION FUND</x:t>
   </x:si>
   <x:si>
     <x:t>H0FL13158</x:t>
@@ -285,8 +294,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J14" totalsRowShown="0">
-  <x:autoFilter ref="A1:J14"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
+  <x:autoFilter ref="A1:J15"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -591,7 +600,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J14"/>
+  <x:dimension ref="A1:J15"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -801,60 +810,60 @@
     </x:row>
     <x:row r="7" spans="1:10">
       <x:c r="A7" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B7" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C7" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>32</x:v>
       </x:c>
       <x:c r="D7" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>33</x:v>
       </x:c>
       <x:c r="E7" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F7" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="G7" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H7" s="1">
-        <x:v>4383749</x:v>
+        <x:v>249314</x:v>
       </x:c>
       <x:c r="I7" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J7" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -865,60 +874,60 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
+        <x:v>37</x:v>
+      </x:c>
+      <x:c r="B9" s="1" t="s">
         <x:v>38</x:v>
       </x:c>
-      <x:c r="B9" s="1" t="s">
+      <x:c r="C9" s="1" t="s">
         <x:v>39</x:v>
       </x:c>
-      <x:c r="C9" s="1" t="s">
+      <x:c r="D9" s="1" t="s">
         <x:v>40</x:v>
       </x:c>
-      <x:c r="D9" s="1" t="s">
+      <x:c r="E9" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F9" s="1" t="s">
         <x:v>41</x:v>
       </x:c>
-      <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F9" s="1" t="s">
+      <x:c r="G9" s="1" t="s">
         <x:v>42</x:v>
       </x:c>
-      <x:c r="G9" s="1" t="s">
-        <x:v>43</x:v>
-      </x:c>
       <x:c r="H9" s="1">
-        <x:v>338408</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
         <x:v>44</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="C10" s="1" t="s">
         <x:v>45</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>46</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
+      <x:c r="G10" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="H10" s="1">
-        <x:v>2326917</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -929,28 +938,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>32</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>33</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -961,34 +970,34 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
@@ -1011,47 +1020,79 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="G14" s="1" t="s">
+      <x:c r="H14" s="1">
+        <x:v>299290</x:v>
+      </x:c>
+      <x:c r="I14" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J14" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:10">
+      <x:c r="A15" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="H14" s="1">
+      <x:c r="D15" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="H15" s="1">
         <x:v>159276</x:v>
       </x:c>
-      <x:c r="I14" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J14" s="1" t="s">
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -145,6 +145,24 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H2VA02064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>KIGGANS, JENNIFER</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VA</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00931774</x:t>
   </x:si>
   <x:si>
@@ -197,9 +215,6 @@
   </x:si>
   <x:si>
     <x:t>MILLER, DONNA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
   </x:si>
   <x:si>
     <x:t>H0FL13158</x:t>
@@ -294,8 +309,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J15" totalsRowShown="0">
-  <x:autoFilter ref="A1:J15"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
+  <x:autoFilter ref="A1:J16"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -600,7 +615,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J15"/>
+  <x:dimension ref="A1:J16"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -927,7 +942,7 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>338408</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -959,7 +974,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>2326917</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -970,28 +985,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1002,97 +1017,129 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H15" s="1">
+        <x:v>299290</x:v>
+      </x:c>
+      <x:c r="I15" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J15" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:10">
+      <x:c r="A16" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="H16" s="1">
         <x:v>159276</x:v>
       </x:c>
-      <x:c r="I15" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J15" s="1" t="s">
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -145,6 +145,24 @@
     <x:t>KY</x:t>
   </x:si>
   <x:si>
+    <x:t>C00931774</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARTICLE ONE PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6TX15162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GONZALEZ, VICENTE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TX</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00710848</x:t>
   </x:si>
   <x:si>
@@ -161,12 +179,6 @@
   </x:si>
   <x:si>
     <x:t>VA</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00931774</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ARTICLE ONE PAC</x:t>
   </x:si>
   <x:si>
     <x:t>H0NY02267</x:t>
@@ -309,8 +321,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J16" totalsRowShown="0">
-  <x:autoFilter ref="A1:J16"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
+  <x:autoFilter ref="A1:J17"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -615,7 +627,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J16"/>
+  <x:dimension ref="A1:J17"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -942,13 +954,13 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>900000</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
@@ -974,7 +986,7 @@
         <x:v>54</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>338408</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -985,28 +997,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="G12" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H12" s="1">
-        <x:v>2326917</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1017,10 +1029,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>61</x:v>
@@ -1032,13 +1044,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1049,10 +1061,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>65</x:v>
@@ -1064,59 +1076,59 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
         <x:v>71</x:v>
@@ -1134,12 +1146,44 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="H16" s="1">
+        <x:v>299290</x:v>
+      </x:c>
+      <x:c r="I16" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J16" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:10">
+      <x:c r="A17" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>44</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G17" s="1" t="s">
+        <x:v>78</x:v>
+      </x:c>
+      <x:c r="H17" s="1">
         <x:v>159276</x:v>
       </x:c>
-      <x:c r="I16" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J16" s="1" t="s">
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -121,6 +121,27 @@
     <x:t>PA</x:t>
   </x:si>
   <x:si>
+    <x:t>C00684969</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JDCA PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OH00163</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BROWN, SHERROD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Senate</x:t>
+  </x:si>
+  <x:si>
+    <x:t>00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OH</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
@@ -161,6 +182,12 @@
   </x:si>
   <x:si>
     <x:t>TX</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6OH00304</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HUSTED, JON</x:t>
   </x:si>
   <x:si>
     <x:t>C00710848</x:t>
@@ -321,8 +348,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J17" totalsRowShown="0">
-  <x:autoFilter ref="A1:J17"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0">
+  <x:autoFilter ref="A1:J19"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -627,7 +654,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J17"/>
+  <x:dimension ref="A1:J19"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -869,28 +896,28 @@
     </x:row>
     <x:row r="8" spans="1:10">
       <x:c r="A8" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B8" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C8" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D8" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E8" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F8" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G8" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H8" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1573</x:v>
       </x:c>
       <x:c r="I8" s="1">
         <x:v>2026</x:v>
@@ -901,28 +928,28 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -933,28 +960,28 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>112350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -965,60 +992,60 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>900000</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>338408</x:v>
+        <x:v>59000</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1029,28 +1056,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="C13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>2326917</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1061,28 +1088,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>37</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>38</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>3232621</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1093,60 +1120,60 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>299290</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1157,33 +1184,97 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H17" s="1">
+        <x:v>4379246</x:v>
+      </x:c>
+      <x:c r="I17" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J17" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:10">
+      <x:c r="A18" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="G18" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="H18" s="1">
+        <x:v>299290</x:v>
+      </x:c>
+      <x:c r="I18" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J18" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:10">
+      <x:c r="A19" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
+        <x:v>85</x:v>
+      </x:c>
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G19" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="H19" s="1">
         <x:v>159276</x:v>
       </x:c>
-      <x:c r="I17" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J17" s="1" t="s">
+      <x:c r="I19" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J19" s="1" t="s">
         <x:v>23</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -142,18 +142,27 @@
     <x:t>OH</x:t>
   </x:si>
   <x:si>
+    <x:t>C00528554</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RJC VICTORY FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6MI00418</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EL-SAYED, ABDUL</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MI</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
     <x:t>FINE, LAURA</x:t>
   </x:si>
   <x:si>
-    <x:t>C00528554</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RJC VICTORY FUND</x:t>
-  </x:si>
-  <x:si>
     <x:t>H6KY04171</x:t>
   </x:si>
   <x:si>
@@ -278,6 +287,15 @@
   </x:si>
   <x:si>
     <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H0WI03175</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VAN ORDEN, DERRICK F. MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WI</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -348,8 +366,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J19" totalsRowShown="0">
-  <x:autoFilter ref="A1:J19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J21" totalsRowShown="0">
+  <x:autoFilter ref="A1:J21"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -654,7 +672,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J19"/>
+  <x:dimension ref="A1:J21"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -928,60 +946,60 @@
     </x:row>
     <x:row r="9" spans="1:10">
       <x:c r="A9" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B9" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C9" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D9" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>4383749</x:v>
+        <x:v>15298</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J9" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -992,28 +1010,28 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="D11" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="E11" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
+      <x:c r="G11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F11" s="1" t="s">
-        <x:v>54</x:v>
-      </x:c>
-      <x:c r="G11" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
       <x:c r="H11" s="1">
-        <x:v>112350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1024,60 +1042,60 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>59000</x:v>
+        <x:v>112350</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
       <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>900000</x:v>
+        <x:v>59000</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1088,28 +1106,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D14" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>338408</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1120,28 +1138,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>2326917</x:v>
+        <x:v>338408</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1152,28 +1170,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>48</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1184,98 +1202,162 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
+      <x:c r="G19" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="G19" s="1" t="s">
+      <x:c r="H19" s="1">
+        <x:v>299290</x:v>
+      </x:c>
+      <x:c r="I19" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J19" s="1" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:10">
+      <x:c r="A20" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="B20" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="H19" s="1">
+      <x:c r="D20" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G20" s="1" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="H20" s="1">
         <x:v>159276</x:v>
       </x:c>
-      <x:c r="I19" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J19" s="1" t="s">
+      <x:c r="I20" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J20" s="1" t="s">
         <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:10">
+      <x:c r="A21" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B21" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H21" s="1">
+        <x:v>299632</x:v>
+      </x:c>
+      <x:c r="I21" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J21" s="1" t="s">
+        <x:v>17</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -287,6 +287,15 @@
   </x:si>
   <x:si>
     <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8CA01109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>THOMPSON, MIKE MR.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
   </x:si>
   <x:si>
     <x:t>H0WI03175</x:t>
@@ -366,8 +375,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J21" totalsRowShown="0">
-  <x:autoFilter ref="A1:J21"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
+  <x:autoFilter ref="A1:J22"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -672,7 +681,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J21"/>
+  <x:dimension ref="A1:J22"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1063,7 +1072,7 @@
         <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>112350</x:v>
+        <x:v>192350</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1159,7 +1168,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>338408</x:v>
+        <x:v>438408</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1330,10 +1339,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>91</x:v>
@@ -1345,18 +1354,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
       <x:c r="H21" s="1">
+        <x:v>399000</x:v>
+      </x:c>
+      <x:c r="I21" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J21" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:10">
+      <x:c r="A22" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="H22" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I21" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J21" s="1" t="s">
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -157,6 +157,12 @@
     <x:t>MI</x:t>
   </x:si>
   <x:si>
+    <x:t>C00799031</x:t>
+  </x:si>
+  <x:si>
+    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
@@ -227,12 +233,6 @@
   </x:si>
   <x:si>
     <x:t>NY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00799031</x:t>
-  </x:si>
-  <x:si>
-    <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
     <x:t>H8NJ07223</x:t>
@@ -375,8 +375,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J22" totalsRowShown="0">
-  <x:autoFilter ref="A1:J22"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
+  <x:autoFilter ref="A1:J23"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -681,7 +681,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J22"/>
+  <x:dimension ref="A1:J23"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -987,42 +987,42 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>4383749</x:v>
+        <x:v>94620</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>49</x:v>
@@ -1034,13 +1034,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1051,28 +1051,28 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="E12" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="G12" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>55</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>57</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="H12" s="1">
-        <x:v>192350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1083,60 +1083,60 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>41</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>59000</x:v>
+        <x:v>192350</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>900000</x:v>
+        <x:v>59000</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1147,28 +1147,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>70</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>438408</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1179,28 +1179,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B16" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="B16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
-        <x:v>73</x:v>
-      </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>74</x:v>
-      </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>2326917</x:v>
+        <x:v>438408</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1211,28 +1211,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1243,124 +1243,124 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>399000</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1371,33 +1371,65 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
+        <x:v>93</x:v>
+      </x:c>
+      <x:c r="H22" s="1">
+        <x:v>399000</x:v>
+      </x:c>
+      <x:c r="I22" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J22" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:10">
+      <x:c r="A23" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="B23" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
+      <x:c r="C23" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
-      <x:c r="G22" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="H22" s="1">
+      <x:c r="H23" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I22" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J22" s="1" t="s">
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1200,7 +1200,7 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>438408</x:v>
+        <x:v>524708</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -976,7 +976,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>15298</x:v>
+        <x:v>1275816</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -140,6 +140,21 @@
   </x:si>
   <x:si>
     <x:t>OH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>C00815753</x:t>
+  </x:si>
+  <x:si>
+    <x:t>J STREET ACTION FUND</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6GA00390</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COLLINS, MICHAEL A JR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GA</x:t>
   </x:si>
   <x:si>
     <x:t>C00528554</x:t>
@@ -375,8 +390,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J23" totalsRowShown="0">
-  <x:autoFilter ref="A1:J23"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
+  <x:autoFilter ref="A1:J24"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -681,7 +696,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J23"/>
+  <x:dimension ref="A1:J24"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -976,7 +991,7 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>1275816</x:v>
+        <x:v>470000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -993,10 +1008,10 @@
         <x:v>48</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>44</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>45</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
         <x:v>39</x:v>
@@ -1005,10 +1020,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>94620</x:v>
+        <x:v>1275816</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1019,10 +1034,10 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B11" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
         <x:v>49</x:v>
@@ -1031,48 +1046,48 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>4383749</x:v>
+        <x:v>94620</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F12" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1083,28 +1098,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>57</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
+      <x:c r="G13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>60</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>192350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1115,60 +1130,60 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>59000</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>900000</x:v>
+        <x:v>59000</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1179,28 +1194,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>524708</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1211,28 +1226,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>2326917</x:v>
+        <x:v>872712</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1243,28 +1258,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1275,124 +1290,124 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>399000</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1403,33 +1418,65 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
+        <x:v>96</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H23" s="1">
+        <x:v>399000</x:v>
+      </x:c>
+      <x:c r="I23" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J23" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:10">
+      <x:c r="A24" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
+      <x:c r="B24" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>96</x:v>
-      </x:c>
-      <x:c r="H23" s="1">
+      <x:c r="C24" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>76</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>101</x:v>
+      </x:c>
+      <x:c r="H24" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I23" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J23" s="1" t="s">
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1055,7 +1055,7 @@
         <x:v>51</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>94620</x:v>
+        <x:v>283860</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -214,6 +214,15 @@
     <x:t>TX</x:t>
   </x:si>
   <x:si>
+    <x:t>H6PA01181</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HARVIE, ROBERT J</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6OH00304</x:t>
   </x:si>
   <x:si>
@@ -296,9 +305,6 @@
   </x:si>
   <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>01</x:t>
   </x:si>
   <x:si>
     <x:t>NH</x:t>
@@ -390,8 +396,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J24" totalsRowShown="0">
-  <x:autoFilter ref="A1:J24"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
+  <x:autoFilter ref="A1:J25"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -696,7 +702,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J24"/>
+  <x:dimension ref="A1:J25"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1162,10 +1168,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>66</x:v>
@@ -1174,16 +1180,16 @@
         <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>59000</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1194,28 +1200,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>900000</x:v>
+        <x:v>59000</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1226,28 +1232,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="D17" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
+      <x:c r="G17" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>872712</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1258,28 +1264,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
+      <x:c r="G18" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>2326917</x:v>
+        <x:v>872712</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1290,28 +1296,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1322,98 +1328,98 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="C20" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="C20" s="1" t="s">
+      <x:c r="D20" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
-        <x:v>87</x:v>
-      </x:c>
       <x:c r="E20" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
+      <x:c r="G22" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
@@ -1424,22 +1430,22 @@
         <x:v>61</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>95</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>98</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>399000</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1450,33 +1456,65 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="B24" s="1" t="s">
+        <x:v>61</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D24" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="E24" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F24" s="1" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="G24" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="H24" s="1">
+        <x:v>500175</x:v>
+      </x:c>
+      <x:c r="I24" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J24" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:10">
+      <x:c r="A25" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B24" s="1" t="s">
+      <x:c r="B25" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
-      <x:c r="E24" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F24" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G24" s="1" t="s">
+      <x:c r="C25" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="H24" s="1">
+      <x:c r="D25" s="1" t="s">
+        <x:v>102</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="H25" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I24" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J24" s="1" t="s">
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -157,6 +157,18 @@
     <x:t>GA</x:t>
   </x:si>
   <x:si>
+    <x:t>H6NY17171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CONLEY, CAIT</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NY</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -254,9 +266,6 @@
   </x:si>
   <x:si>
     <x:t>03</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NY</x:t>
   </x:si>
   <x:si>
     <x:t>H8NJ07223</x:t>
@@ -396,8 +405,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J25" totalsRowShown="0">
-  <x:autoFilter ref="A1:J25"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
+  <x:autoFilter ref="A1:J26"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -702,7 +711,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J25"/>
+  <x:dimension ref="A1:J26"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1008,48 +1017,48 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B10" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C10" s="1" t="s">
         <x:v>47</x:v>
       </x:c>
-      <x:c r="B10" s="1" t="s">
+      <x:c r="D10" s="1" t="s">
         <x:v>48</x:v>
       </x:c>
-      <x:c r="C10" s="1" t="s">
+      <x:c r="E10" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F10" s="1" t="s">
         <x:v>49</x:v>
       </x:c>
-      <x:c r="D10" s="1" t="s">
+      <x:c r="G10" s="1" t="s">
         <x:v>50</x:v>
       </x:c>
-      <x:c r="E10" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F10" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G10" s="1" t="s">
-        <x:v>51</x:v>
-      </x:c>
       <x:c r="H10" s="1">
-        <x:v>1275816</x:v>
+        <x:v>49994</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
         <x:v>52</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="C11" s="1" t="s">
         <x:v>53</x:v>
       </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>49</x:v>
-      </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>39</x:v>
@@ -1058,10 +1067,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>283860</x:v>
+        <x:v>1275816</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1072,60 +1081,60 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D12" s="1" t="s">
         <x:v>54</x:v>
       </x:c>
-      <x:c r="D12" s="1" t="s">
+      <x:c r="E12" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F12" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G12" s="1" t="s">
         <x:v>55</x:v>
       </x:c>
-      <x:c r="E12" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F12" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G12" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H12" s="1">
-        <x:v>4383749</x:v>
+        <x:v>283860</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1136,28 +1145,28 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
         <x:v>62</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="G14" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>432350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1168,10 +1177,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>66</x:v>
@@ -1186,42 +1195,42 @@
         <x:v>68</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>383500</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>59000</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1232,10 +1241,10 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>73</x:v>
@@ -1244,16 +1253,16 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>900000</x:v>
+        <x:v>59000</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1264,10 +1273,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>77</x:v>
@@ -1285,7 +1294,7 @@
         <x:v>80</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>872712</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1296,10 +1305,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>81</x:v>
@@ -1314,10 +1323,10 @@
         <x:v>83</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>2326917</x:v>
+        <x:v>872712</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1328,28 +1337,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>86</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>58</x:v>
-      </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1360,106 +1369,106 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C21" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="C21" s="1" t="s">
+      <x:c r="D21" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
-        <x:v>90</x:v>
-      </x:c>
       <x:c r="E21" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J21" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
         <x:v>96</x:v>
-      </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>68</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>98</x:v>
@@ -1471,13 +1480,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>500175</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1488,10 +1497,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>101</x:v>
@@ -1503,18 +1512,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
       <x:c r="H25" s="1">
+        <x:v>500175</x:v>
+      </x:c>
+      <x:c r="I25" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J25" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:10">
+      <x:c r="A26" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="H26" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I25" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J25" s="1" t="s">
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1102,7 +1102,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>283860</x:v>
+        <x:v>378480</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -268,15 +268,21 @@
     <x:t>03</x:t>
   </x:si>
   <x:si>
+    <x:t>H8PA15195</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MACKENZIE, RYAN EDWARD</x:t>
+  </x:si>
+  <x:si>
+    <x:t>07</x:t>
+  </x:si>
+  <x:si>
     <x:t>H8NJ07223</x:t>
   </x:si>
   <x:si>
     <x:t>MALINOWSKI, TOM</x:t>
   </x:si>
   <x:si>
-    <x:t>07</x:t>
-  </x:si>
-  <x:si>
     <x:t>NJ</x:t>
   </x:si>
   <x:si>
@@ -296,6 +302,15 @@
   </x:si>
   <x:si>
     <x:t>MILLER, DONNA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H8IA02043</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MILLER-MEEKS, MARIANNETTE JANE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IA</x:t>
   </x:si>
   <x:si>
     <x:t>H0FL13158</x:t>
@@ -405,8 +420,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J26" totalsRowShown="0">
-  <x:autoFilter ref="A1:J26"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
+  <x:autoFilter ref="A1:J28"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -711,14 +726,14 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J26"/>
+  <x:dimension ref="A1:J28"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
     <x:col min="1" max="1" width="15.710625" style="1" customWidth="1"/>
     <x:col min="2" max="2" width="35.282054" style="1" customWidth="1"/>
     <x:col min="3" max="3" width="14.853482" style="1" customWidth="1"/>
-    <x:col min="4" max="4" width="28.424911" style="1" customWidth="1"/>
+    <x:col min="4" max="4" width="33.567768" style="1" customWidth="1"/>
     <x:col min="5" max="5" width="17.853482" style="1" customWidth="1"/>
     <x:col min="6" max="6" width="25.282054" style="1" customWidth="1"/>
     <x:col min="7" max="7" width="23.424911" style="1" customWidth="1"/>
@@ -1070,7 +1085,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1275816</x:v>
+        <x:v>1331252</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1326,7 +1341,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>872712</x:v>
+        <x:v>1433710</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1337,10 +1352,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>84</x:v>
@@ -1355,10 +1370,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>2326917</x:v>
+        <x:v>278582</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1369,28 +1384,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>87</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>89</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H21" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1401,42 +1416,42 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B22" s="1" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C22" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="B22" s="1" t="s">
+      <x:c r="D22" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="C22" s="1" t="s">
-        <x:v>92</x:v>
-      </x:c>
-      <x:c r="D22" s="1" t="s">
-        <x:v>93</x:v>
-      </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>4379246</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>94</x:v>
@@ -1448,33 +1463,33 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
@@ -1483,79 +1498,143 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>159276</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>99</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
+        <x:v>100</x:v>
+      </x:c>
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="G25" s="1" t="s">
         <x:v>102</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>103</x:v>
-      </x:c>
       <x:c r="H25" s="1">
-        <x:v>500175</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B26" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D26" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="E26" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F26" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G26" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="H26" s="1">
+        <x:v>159276</x:v>
+      </x:c>
+      <x:c r="I26" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J26" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:10">
+      <x:c r="A27" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B27" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D27" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E27" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F27" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="H27" s="1">
+        <x:v>695175</x:v>
+      </x:c>
+      <x:c r="I27" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J27" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:10">
+      <x:c r="A28" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B26" s="1" t="s">
+      <x:c r="B28" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
-      <x:c r="E26" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F26" s="1" t="s">
+      <x:c r="C28" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G26" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="H26" s="1">
+      <x:c r="G28" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I26" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J26" s="1" t="s">
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -290,6 +290,12 @@
   </x:si>
   <x:si>
     <x:t>MASSIE, THOMAS H.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4OH09169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MERRIN, DEREK</x:t>
   </x:si>
   <x:si>
     <x:t>C00935049</x:t>
@@ -420,8 +426,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J28" totalsRowShown="0">
-  <x:autoFilter ref="A1:J28"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
+  <x:autoFilter ref="A1:J30"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -726,7 +732,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J28"/>
+  <x:dimension ref="A1:J30"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1117,7 +1123,7 @@
         <x:v>55</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>378480</x:v>
+        <x:v>493302</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1448,42 +1454,42 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B23" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C23" s="1" t="s">
         <x:v>92</x:v>
       </x:c>
-      <x:c r="B23" s="1" t="s">
+      <x:c r="D23" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="C23" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="D23" s="1" t="s">
-        <x:v>95</x:v>
-      </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>4379246</x:v>
+        <x:v>181101</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J23" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>96</x:v>
@@ -1495,19 +1501,19 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>218493</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
@@ -1518,22 +1524,22 @@
         <x:v>31</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="D25" s="1" t="s">
         <x:v>99</x:v>
       </x:c>
-      <x:c r="D25" s="1" t="s">
+      <x:c r="E25" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F25" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G25" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="E25" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F25" s="1" t="s">
-        <x:v>101</x:v>
-      </x:c>
-      <x:c r="G25" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="H25" s="1">
-        <x:v>299290</x:v>
+        <x:v>131844</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1544,16 +1550,16 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
@@ -1562,79 +1568,143 @@
         <x:v>72</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>159276</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>695175</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B28" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C28" s="1" t="s">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="H28" s="1">
+        <x:v>159276</x:v>
+      </x:c>
+      <x:c r="I28" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J28" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:10">
+      <x:c r="A29" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="B29" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="C29" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="H29" s="1">
+        <x:v>744702</x:v>
+      </x:c>
+      <x:c r="I29" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J29" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:10">
+      <x:c r="A30" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B28" s="1" t="s">
+      <x:c r="B30" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C28" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
+      <x:c r="C30" s="1" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>111</x:v>
-      </x:c>
-      <x:c r="H28" s="1">
+      <x:c r="G30" s="1" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I28" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J28" s="1" t="s">
+      <x:c r="I30" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -169,6 +169,15 @@
     <x:t>NY</x:t>
   </x:si>
   <x:si>
+    <x:t>S6NC00407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>COOPER, ROY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -338,6 +347,18 @@
   </x:si>
   <x:si>
     <x:t>NH</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H6NY03247</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUOZZI, THOMAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>S6TX00479</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TALARICO, JAMES</x:t>
   </x:si>
   <x:si>
     <x:t>H8CA01109</x:t>
@@ -426,8 +447,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J30" totalsRowShown="0">
-  <x:autoFilter ref="A1:J30"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J33" totalsRowShown="0">
+  <x:autoFilter ref="A1:J33"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -732,7 +753,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J30"/>
+  <x:dimension ref="A1:J33"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1059,7 +1080,7 @@
         <x:v>50</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>49994</x:v>
+        <x:v>67013</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
@@ -1070,16 +1091,16 @@
     </x:row>
     <x:row r="11" spans="1:10">
       <x:c r="A11" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B11" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C11" s="1" t="s">
         <x:v>51</x:v>
       </x:c>
-      <x:c r="B11" s="1" t="s">
+      <x:c r="D11" s="1" t="s">
         <x:v>52</x:v>
-      </x:c>
-      <x:c r="C11" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D11" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
         <x:v>39</x:v>
@@ -1088,30 +1109,30 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1331252</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J11" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B12" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C12" s="1" t="s">
         <x:v>56</x:v>
       </x:c>
-      <x:c r="B12" s="1" t="s">
+      <x:c r="D12" s="1" t="s">
         <x:v>57</x:v>
-      </x:c>
-      <x:c r="C12" s="1" t="s">
-        <x:v>53</x:v>
-      </x:c>
-      <x:c r="D12" s="1" t="s">
-        <x:v>54</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>39</x:v>
@@ -1120,10 +1141,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>493302</x:v>
+        <x:v>1331252</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
@@ -1134,60 +1155,60 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="D13" s="1" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="E13" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>58</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>59</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>16</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>4383749</x:v>
+        <x:v>587922</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D14" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1198,28 +1219,28 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="C15" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="E15" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
+      <x:c r="G15" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>432350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1230,42 +1251,42 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>34</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>383500</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>73</x:v>
@@ -1274,16 +1295,16 @@
         <x:v>74</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>59000</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1294,28 +1315,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="D18" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>78</x:v>
-      </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>900000</x:v>
+        <x:v>83118</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1326,28 +1347,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
+      <x:c r="G19" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>1433710</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1358,10 +1379,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>84</x:v>
@@ -1376,10 +1397,10 @@
         <x:v>86</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>278582</x:v>
+        <x:v>1433710</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1390,10 +1411,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>87</x:v>
@@ -1405,13 +1426,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>2326917</x:v>
+        <x:v>278582</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1422,10 +1443,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>90</x:v>
@@ -1437,13 +1458,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1454,28 +1475,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>181101</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1486,92 +1507,92 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C24" s="1" t="s">
         <x:v>95</x:v>
       </x:c>
-      <x:c r="C24" s="1" t="s">
+      <x:c r="D24" s="1" t="s">
         <x:v>96</x:v>
       </x:c>
-      <x:c r="D24" s="1" t="s">
-        <x:v>97</x:v>
-      </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>4379246</x:v>
+        <x:v>181101</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J24" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>131844</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>218493</x:v>
+        <x:v>131844</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1582,10 +1603,10 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
         <x:v>101</x:v>
@@ -1597,13 +1618,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="G27" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="G27" s="1" t="s">
-        <x:v>104</x:v>
-      </x:c>
       <x:c r="H27" s="1">
-        <x:v>299290</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1614,42 +1635,42 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>106</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>72</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>108</x:v>
@@ -1661,13 +1682,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>744702</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1678,10 +1699,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>111</x:v>
@@ -1693,18 +1714,114 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
+        <x:v>50</x:v>
+      </x:c>
+      <x:c r="H30" s="1">
+        <x:v>16000</x:v>
+      </x:c>
+      <x:c r="I30" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J30" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:10">
+      <x:c r="A31" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B31" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C31" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="H30" s="1">
+      <x:c r="D31" s="1" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="E31" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G31" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="H31" s="1">
+        <x:v>60064</x:v>
+      </x:c>
+      <x:c r="I31" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J31" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:10">
+      <x:c r="A32" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="B32" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="C32" s="1" t="s">
+        <x:v>115</x:v>
+      </x:c>
+      <x:c r="D32" s="1" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="E32" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F32" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G32" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="H32" s="1">
+        <x:v>744702</x:v>
+      </x:c>
+      <x:c r="I32" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J32" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:10">
+      <x:c r="A33" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="H33" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I30" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J30" s="1" t="s">
+      <x:c r="I33" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -142,6 +142,24 @@
     <x:t>OH</x:t>
   </x:si>
   <x:si>
+    <x:t>C00710848</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DMFI PAC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>H4NC01137</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BUCKHOUT, LAURIE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>01</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NC</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00815753</x:t>
   </x:si>
   <x:si>
@@ -175,9 +193,6 @@
     <x:t>COOPER, ROY</x:t>
   </x:si>
   <x:si>
-    <x:t>NC</x:t>
-  </x:si>
-  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -241,19 +256,10 @@
     <x:t>HARVIE, ROBERT J</x:t>
   </x:si>
   <x:si>
-    <x:t>01</x:t>
-  </x:si>
-  <x:si>
     <x:t>S6OH00304</x:t>
   </x:si>
   <x:si>
     <x:t>HUSTED, JON</x:t>
-  </x:si>
-  <x:si>
-    <x:t>C00710848</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DMFI PAC</x:t>
   </x:si>
   <x:si>
     <x:t>H2VA02064</x:t>
@@ -447,8 +453,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J33" totalsRowShown="0">
-  <x:autoFilter ref="A1:J33"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J34" totalsRowShown="0">
+  <x:autoFilter ref="A1:J34"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -753,7 +759,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J33"/>
+  <x:dimension ref="A1:J34"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1039,16 +1045,16 @@
         <x:v>45</x:v>
       </x:c>
       <x:c r="E9" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F9" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G9" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H9" s="1">
-        <x:v>470000</x:v>
+        <x:v>4950000</x:v>
       </x:c>
       <x:c r="I9" s="1">
         <x:v>2026</x:v>
@@ -1059,34 +1065,34 @@
     </x:row>
     <x:row r="10" spans="1:10">
       <x:c r="A10" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B10" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C10" s="1" t="s">
-        <x:v>47</x:v>
+        <x:v>50</x:v>
       </x:c>
       <x:c r="D10" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="E10" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F10" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G10" s="1" t="s">
-        <x:v>50</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="H10" s="1">
-        <x:v>67013</x:v>
+        <x:v>470000</x:v>
       </x:c>
       <x:c r="I10" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J10" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="11" spans="1:10">
@@ -1097,22 +1103,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C11" s="1" t="s">
-        <x:v>51</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D11" s="1" t="s">
-        <x:v>52</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E11" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F11" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="G11" s="1" t="s">
-        <x:v>53</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>1003</x:v>
+        <x:v>67013</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1123,16 +1129,16 @@
     </x:row>
     <x:row r="12" spans="1:10">
       <x:c r="A12" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B12" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C12" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>57</x:v>
       </x:c>
       <x:c r="D12" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>58</x:v>
       </x:c>
       <x:c r="E12" s="1" t="s">
         <x:v>39</x:v>
@@ -1141,16 +1147,16 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G12" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="H12" s="1">
-        <x:v>1331252</x:v>
+        <x:v>1003</x:v>
       </x:c>
       <x:c r="I12" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J12" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="13" spans="1:10">
@@ -1161,10 +1167,10 @@
         <x:v>60</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="D13" s="1" t="s">
-        <x:v>57</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="E13" s="1" t="s">
         <x:v>39</x:v>
@@ -1173,10 +1179,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>58</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>587922</x:v>
+        <x:v>1331252</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1187,10 +1193,10 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C14" s="1" t="s">
         <x:v>61</x:v>
@@ -1199,48 +1205,48 @@
         <x:v>62</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F14" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>4383749</x:v>
+        <x:v>587922</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J14" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1251,28 +1257,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C16" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C16" s="1" t="s">
+      <x:c r="D16" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
+      <x:c r="G16" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>432350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1283,60 +1289,60 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>383500</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J17" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>83118</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1347,10 +1353,10 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
         <x:v>80</x:v>
@@ -1359,16 +1365,16 @@
         <x:v>81</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>900000</x:v>
+        <x:v>83118</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1379,28 +1385,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="D20" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="E20" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F20" s="1" t="s">
         <x:v>84</x:v>
       </x:c>
-      <x:c r="D20" s="1" t="s">
+      <x:c r="G20" s="1" t="s">
         <x:v>85</x:v>
       </x:c>
-      <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F20" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G20" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="H20" s="1">
-        <x:v>1433710</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1411,28 +1417,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
+        <x:v>86</x:v>
+      </x:c>
+      <x:c r="D21" s="1" t="s">
         <x:v>87</x:v>
       </x:c>
-      <x:c r="D21" s="1" t="s">
+      <x:c r="E21" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F21" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F21" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>278582</x:v>
+        <x:v>1433710</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1443,28 +1449,28 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="D22" s="1" t="s">
         <x:v>90</x:v>
       </x:c>
-      <x:c r="D22" s="1" t="s">
+      <x:c r="E22" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F22" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="E22" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F22" s="1" t="s">
-        <x:v>89</x:v>
-      </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>2326917</x:v>
+        <x:v>278582</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1475,28 +1481,28 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>54</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>55</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
+        <x:v>92</x:v>
+      </x:c>
+      <x:c r="D23" s="1" t="s">
         <x:v>93</x:v>
       </x:c>
-      <x:c r="D23" s="1" t="s">
+      <x:c r="E23" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F23" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G23" s="1" t="s">
         <x:v>94</x:v>
       </x:c>
-      <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F23" s="1" t="s">
-        <x:v>65</x:v>
-      </x:c>
-      <x:c r="G23" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="H23" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1507,10 +1513,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>95</x:v>
@@ -1522,13 +1528,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>181101</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1539,42 +1545,42 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B25" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C25" s="1" t="s">
         <x:v>97</x:v>
       </x:c>
-      <x:c r="B25" s="1" t="s">
+      <x:c r="D25" s="1" t="s">
         <x:v>98</x:v>
       </x:c>
-      <x:c r="C25" s="1" t="s">
-        <x:v>99</x:v>
-      </x:c>
-      <x:c r="D25" s="1" t="s">
-        <x:v>100</x:v>
-      </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>4379246</x:v>
+        <x:v>181101</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J25" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
         <x:v>101</x:v>
@@ -1586,45 +1592,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>131844</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>218493</x:v>
+        <x:v>131844</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1635,28 +1641,28 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>103</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G28" s="1" t="s">
         <x:v>105</x:v>
       </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>106</x:v>
-      </x:c>
-      <x:c r="G28" s="1" t="s">
-        <x:v>107</x:v>
-      </x:c>
       <x:c r="H28" s="1">
-        <x:v>299290</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1667,60 +1673,60 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="D29" s="1" t="s">
+        <x:v>107</x:v>
+      </x:c>
+      <x:c r="E29" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F29" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="D29" s="1" t="s">
+      <x:c r="G29" s="1" t="s">
         <x:v>109</x:v>
       </x:c>
-      <x:c r="E29" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F29" s="1" t="s">
-        <x:v>75</x:v>
-      </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>110</x:v>
-      </x:c>
       <x:c r="H29" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J29" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>50</x:v>
-      </x:c>
       <x:c r="H30" s="1">
-        <x:v>16000</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1731,10 +1737,10 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>113</x:v>
@@ -1743,16 +1749,16 @@
         <x:v>114</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>60064</x:v>
+        <x:v>16000</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1763,10 +1769,10 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>115</x:v>
@@ -1775,16 +1781,16 @@
         <x:v>116</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>744702</x:v>
+        <x:v>60064</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1795,33 +1801,65 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="B33" s="1" t="s">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="C33" s="1" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="D33" s="1" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="E33" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F33" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="G33" s="1" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="H33" s="1">
+        <x:v>794229</x:v>
+      </x:c>
+      <x:c r="I33" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J33" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:10">
+      <x:c r="A34" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B33" s="1" t="s">
+      <x:c r="B34" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C33" s="1" t="s">
-        <x:v>118</x:v>
-      </x:c>
-      <x:c r="D33" s="1" t="s">
-        <x:v>119</x:v>
-      </x:c>
-      <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F33" s="1" t="s">
-        <x:v>86</x:v>
-      </x:c>
-      <x:c r="G33" s="1" t="s">
+      <x:c r="C34" s="1" t="s">
         <x:v>120</x:v>
       </x:c>
-      <x:c r="H33" s="1">
+      <x:c r="D34" s="1" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="E34" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F34" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="G34" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="H34" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I33" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J33" s="1" t="s">
+      <x:c r="I34" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J34" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -214,6 +214,18 @@
     <x:t>UNITED DEMOCRACY PROJECT ('UDP')</x:t>
   </x:si>
   <x:si>
+    <x:t>H4AL02170</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FIGURES, SHOMARI C.</x:t>
+  </x:si>
+  <x:si>
+    <x:t>02</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AL</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6IL09194</x:t>
   </x:si>
   <x:si>
@@ -266,9 +278,6 @@
   </x:si>
   <x:si>
     <x:t>KIGGANS, JENNIFER</x:t>
-  </x:si>
-  <x:si>
-    <x:t>02</x:t>
   </x:si>
   <x:si>
     <x:t>VA</x:t>
@@ -453,8 +462,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J34" totalsRowShown="0">
-  <x:autoFilter ref="A1:J34"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J35" totalsRowShown="0">
+  <x:autoFilter ref="A1:J35"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -759,7 +768,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J34"/>
+  <x:dimension ref="A1:J35"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1225,10 +1234,10 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
         <x:v>66</x:v>
@@ -1240,13 +1249,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F15" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1999145</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1257,28 +1266,28 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D16" s="1" t="s">
-        <x:v>69</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E16" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F16" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1289,28 +1298,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
+        <x:v>59</x:v>
+      </x:c>
+      <x:c r="B17" s="1" t="s">
+        <x:v>60</x:v>
+      </x:c>
+      <x:c r="C17" s="1" t="s">
         <x:v>72</x:v>
       </x:c>
-      <x:c r="B17" s="1" t="s">
+      <x:c r="D17" s="1" t="s">
         <x:v>73</x:v>
       </x:c>
-      <x:c r="C17" s="1" t="s">
+      <x:c r="E17" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F17" s="1" t="s">
         <x:v>74</x:v>
       </x:c>
-      <x:c r="D17" s="1" t="s">
+      <x:c r="G17" s="1" t="s">
         <x:v>75</x:v>
       </x:c>
-      <x:c r="E17" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F17" s="1" t="s">
-        <x:v>76</x:v>
-      </x:c>
-      <x:c r="G17" s="1" t="s">
-        <x:v>77</x:v>
-      </x:c>
       <x:c r="H17" s="1">
-        <x:v>432350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1321,10 +1330,10 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
         <x:v>78</x:v>
@@ -1336,45 +1345,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>383500</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J18" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="D19" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="E19" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F19" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>83118</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1385,28 +1394,28 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>82</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>83</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>900000</x:v>
+        <x:v>83118</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1417,10 +1426,10 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
         <x:v>86</x:v>
@@ -1432,13 +1441,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="G21" s="1" t="s">
         <x:v>88</x:v>
       </x:c>
-      <x:c r="G21" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H21" s="1">
-        <x:v>1433710</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1449,10 +1458,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>89</x:v>
@@ -1467,10 +1476,10 @@
         <x:v>91</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>278582</x:v>
+        <x:v>1433710</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1481,10 +1490,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>92</x:v>
@@ -1496,13 +1505,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>2326917</x:v>
+        <x:v>278582</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1513,10 +1522,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>65</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>95</x:v>
@@ -1528,13 +1537,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1545,28 +1554,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>59</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>181101</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1577,80 +1586,80 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C26" s="1" t="s">
         <x:v>100</x:v>
       </x:c>
-      <x:c r="C26" s="1" t="s">
+      <x:c r="D26" s="1" t="s">
         <x:v>101</x:v>
       </x:c>
-      <x:c r="D26" s="1" t="s">
-        <x:v>102</x:v>
-      </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>4379246</x:v>
+        <x:v>181101</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J26" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>131844</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
@@ -1659,10 +1668,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>218493</x:v>
+        <x:v>131844</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
@@ -1673,10 +1682,10 @@
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
         <x:v>106</x:v>
@@ -1688,13 +1697,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G29" s="1" t="s">
         <x:v>108</x:v>
       </x:c>
-      <x:c r="G29" s="1" t="s">
-        <x:v>109</x:v>
-      </x:c>
       <x:c r="H29" s="1">
-        <x:v>299290</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1705,42 +1714,42 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="D30" s="1" t="s">
         <x:v>110</x:v>
       </x:c>
-      <x:c r="D30" s="1" t="s">
+      <x:c r="E30" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F30" s="1" t="s">
         <x:v>111</x:v>
-      </x:c>
-      <x:c r="E30" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F30" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
         <x:v>112</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J30" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
         <x:v>113</x:v>
@@ -1752,13 +1761,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>16000</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
@@ -1769,28 +1778,28 @@
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>60064</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1801,28 +1810,28 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>70</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>794229</x:v>
+        <x:v>60064</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1833,10 +1842,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>120</x:v>
@@ -1848,18 +1857,50 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
         <x:v>122</x:v>
       </x:c>
       <x:c r="H34" s="1">
+        <x:v>794229</x:v>
+      </x:c>
+      <x:c r="I34" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J34" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:10">
+      <x:c r="A35" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>91</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>125</x:v>
+      </x:c>
+      <x:c r="H35" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I34" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J34" s="1" t="s">
+      <x:c r="I35" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J35" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -193,6 +193,15 @@
     <x:t>COOPER, ROY</x:t>
   </x:si>
   <x:si>
+    <x:t>H6NH01420</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DILORENZO, ANTHONY</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NH</x:t>
+  </x:si>
+  <x:si>
     <x:t>C00528554</x:t>
   </x:si>
   <x:si>
@@ -359,9 +368,6 @@
   </x:si>
   <x:si>
     <x:t>SHAHEEN, STEFANY</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NH</x:t>
   </x:si>
   <x:si>
     <x:t>H6NY03247</x:t>
@@ -462,8 +468,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J35" totalsRowShown="0">
-  <x:autoFilter ref="A1:J35"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J36" totalsRowShown="0">
+  <x:autoFilter ref="A1:J36"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -768,7 +774,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J35"/>
+  <x:dimension ref="A1:J36"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1127,7 +1133,7 @@
         <x:v>56</x:v>
       </x:c>
       <x:c r="H11" s="1">
-        <x:v>67013</x:v>
+        <x:v>68216</x:v>
       </x:c>
       <x:c r="I11" s="1">
         <x:v>2026</x:v>
@@ -1170,28 +1176,28 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
+        <x:v>30</x:v>
+      </x:c>
+      <x:c r="B13" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C13" s="1" t="s">
         <x:v>59</x:v>
       </x:c>
-      <x:c r="B13" s="1" t="s">
+      <x:c r="D13" s="1" t="s">
         <x:v>60</x:v>
       </x:c>
-      <x:c r="C13" s="1" t="s">
+      <x:c r="E13" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F13" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G13" s="1" t="s">
         <x:v>61</x:v>
       </x:c>
-      <x:c r="D13" s="1" t="s">
-        <x:v>62</x:v>
-      </x:c>
-      <x:c r="E13" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F13" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G13" s="1" t="s">
-        <x:v>63</x:v>
-      </x:c>
       <x:c r="H13" s="1">
-        <x:v>1331252</x:v>
+        <x:v>760499</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
@@ -1202,16 +1208,16 @@
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B14" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="B14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>65</x:v>
-      </x:c>
-      <x:c r="C14" s="1" t="s">
-        <x:v>61</x:v>
-      </x:c>
-      <x:c r="D14" s="1" t="s">
-        <x:v>62</x:v>
       </x:c>
       <x:c r="E14" s="1" t="s">
         <x:v>39</x:v>
@@ -1220,10 +1226,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G14" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="H14" s="1">
-        <x:v>587922</x:v>
+        <x:v>1331252</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1234,60 +1240,60 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B15" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C15" s="1" t="s">
+        <x:v>64</x:v>
+      </x:c>
+      <x:c r="D15" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="E15" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F15" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G15" s="1" t="s">
         <x:v>66</x:v>
       </x:c>
-      <x:c r="D15" s="1" t="s">
-        <x:v>67</x:v>
-      </x:c>
-      <x:c r="E15" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F15" s="1" t="s">
-        <x:v>68</x:v>
-      </x:c>
-      <x:c r="G15" s="1" t="s">
-        <x:v>69</x:v>
-      </x:c>
       <x:c r="H15" s="1">
-        <x:v>1999145</x:v>
+        <x:v>587922</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J15" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>69</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
         <x:v>71</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>15</x:v>
-      </x:c>
       <x:c r="G16" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1999145</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
@@ -1298,28 +1304,28 @@
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
-        <x:v>72</x:v>
+        <x:v>73</x:v>
       </x:c>
       <x:c r="D17" s="1" t="s">
-        <x:v>73</x:v>
+        <x:v>74</x:v>
       </x:c>
       <x:c r="E17" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1330,28 +1336,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
+        <x:v>62</x:v>
+      </x:c>
+      <x:c r="B18" s="1" t="s">
+        <x:v>63</x:v>
+      </x:c>
+      <x:c r="C18" s="1" t="s">
+        <x:v>75</x:v>
+      </x:c>
+      <x:c r="D18" s="1" t="s">
         <x:v>76</x:v>
       </x:c>
-      <x:c r="B18" s="1" t="s">
+      <x:c r="E18" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F18" s="1" t="s">
         <x:v>77</x:v>
       </x:c>
-      <x:c r="C18" s="1" t="s">
+      <x:c r="G18" s="1" t="s">
         <x:v>78</x:v>
       </x:c>
-      <x:c r="D18" s="1" t="s">
-        <x:v>79</x:v>
-      </x:c>
-      <x:c r="E18" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F18" s="1" t="s">
-        <x:v>80</x:v>
-      </x:c>
-      <x:c r="G18" s="1" t="s">
-        <x:v>81</x:v>
-      </x:c>
       <x:c r="H18" s="1">
-        <x:v>432350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1362,60 +1368,60 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B19" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C19" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="D19" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>83</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>46</x:v>
-      </x:c>
       <x:c r="G19" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H19" s="1">
-        <x:v>383500</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J19" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="D20" s="1" t="s">
-        <x:v>85</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="E20" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>83118</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
@@ -1426,28 +1432,28 @@
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>86</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>900000</x:v>
+        <x:v>83118</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1458,10 +1464,10 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
         <x:v>89</x:v>
@@ -1473,13 +1479,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="G22" s="1" t="s">
         <x:v>91</x:v>
       </x:c>
-      <x:c r="G22" s="1" t="s">
-        <x:v>56</x:v>
-      </x:c>
       <x:c r="H22" s="1">
-        <x:v>1433710</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
@@ -1490,10 +1496,10 @@
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
         <x:v>92</x:v>
@@ -1508,10 +1514,10 @@
         <x:v>94</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>278582</x:v>
+        <x:v>1433710</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1522,10 +1528,10 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>64</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
         <x:v>95</x:v>
@@ -1537,13 +1543,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>2326917</x:v>
+        <x:v>278582</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1554,10 +1560,10 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>59</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>60</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
         <x:v>98</x:v>
@@ -1569,13 +1575,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>3232621</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1586,28 +1592,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>181101</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1618,80 +1624,80 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C27" s="1" t="s">
         <x:v>103</x:v>
       </x:c>
-      <x:c r="C27" s="1" t="s">
+      <x:c r="D27" s="1" t="s">
         <x:v>104</x:v>
       </x:c>
-      <x:c r="D27" s="1" t="s">
-        <x:v>105</x:v>
-      </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>4379246</x:v>
+        <x:v>347351</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J27" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="D28" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="E28" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F28" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>131844</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>107</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
@@ -1700,10 +1706,10 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>108</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>218493</x:v>
+        <x:v>224344</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1714,10 +1720,10 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
         <x:v>109</x:v>
@@ -1729,13 +1735,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G30" s="1" t="s">
         <x:v>111</x:v>
       </x:c>
-      <x:c r="G30" s="1" t="s">
-        <x:v>112</x:v>
-      </x:c>
       <x:c r="H30" s="1">
-        <x:v>299290</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1746,42 +1752,42 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="D31" s="1" t="s">
         <x:v>113</x:v>
       </x:c>
-      <x:c r="D31" s="1" t="s">
+      <x:c r="E31" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F31" s="1" t="s">
         <x:v>114</x:v>
-      </x:c>
-      <x:c r="E31" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F31" s="1" t="s">
-        <x:v>46</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
         <x:v>115</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>159276</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
         <x:v>116</x:v>
@@ -1793,13 +1799,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F32" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>19000</x:v>
+        <x:v>159276</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
@@ -1810,10 +1816,10 @@
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
         <x:v>118</x:v>
@@ -1822,16 +1828,16 @@
         <x:v>119</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>81</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>60064</x:v>
+        <x:v>19000</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
@@ -1842,10 +1848,10 @@
     </x:row>
     <x:row r="34" spans="1:10">
       <x:c r="A34" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B34" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
         <x:v>120</x:v>
@@ -1854,16 +1860,16 @@
         <x:v>121</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>74</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>794229</x:v>
+        <x:v>60064</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1874,33 +1880,65 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
+        <x:v>79</x:v>
+      </x:c>
+      <x:c r="B35" s="1" t="s">
+        <x:v>80</x:v>
+      </x:c>
+      <x:c r="C35" s="1" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="D35" s="1" t="s">
+        <x:v>123</x:v>
+      </x:c>
+      <x:c r="E35" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F35" s="1" t="s">
+        <x:v>77</x:v>
+      </x:c>
+      <x:c r="G35" s="1" t="s">
+        <x:v>124</x:v>
+      </x:c>
+      <x:c r="H35" s="1">
+        <x:v>794229</x:v>
+      </x:c>
+      <x:c r="I35" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J35" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:10">
+      <x:c r="A36" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B35" s="1" t="s">
+      <x:c r="B36" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C35" s="1" t="s">
-        <x:v>123</x:v>
-      </x:c>
-      <x:c r="D35" s="1" t="s">
-        <x:v>124</x:v>
-      </x:c>
-      <x:c r="E35" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F35" s="1" t="s">
-        <x:v>91</x:v>
-      </x:c>
-      <x:c r="G35" s="1" t="s">
+      <x:c r="C36" s="1" t="s">
         <x:v>125</x:v>
       </x:c>
-      <x:c r="H35" s="1">
+      <x:c r="D36" s="1" t="s">
+        <x:v>126</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>94</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>127</x:v>
+      </x:c>
+      <x:c r="H36" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I35" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J35" s="1" t="s">
+      <x:c r="I36" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J36" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -193,6 +193,18 @@
     <x:t>COOPER, ROY</x:t>
   </x:si>
   <x:si>
+    <x:t>H6FL21059</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DANDIYA, PIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>21</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FL</x:t>
+  </x:si>
+  <x:si>
     <x:t>H6NH01420</x:t>
   </x:si>
   <x:si>
@@ -277,12 +289,30 @@
     <x:t>HARVIE, ROBERT J</x:t>
   </x:si>
   <x:si>
+    <x:t>H6MI10276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HINES, CHRISTINA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10</x:t>
+  </x:si>
+  <x:si>
     <x:t>S6OH00304</x:t>
   </x:si>
   <x:si>
     <x:t>HUSTED, JON</x:t>
   </x:si>
   <x:si>
+    <x:t>H6CA04222</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JONES, ERIC</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CA</x:t>
+  </x:si>
+  <x:si>
     <x:t>H2VA02064</x:t>
   </x:si>
   <x:si>
@@ -352,6 +382,15 @@
     <x:t>IA</x:t>
   </x:si>
   <x:si>
+    <x:t>H2FL22171</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MOSKOWITZ, JARED</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23</x:t>
+  </x:si>
+  <x:si>
     <x:t>H0FL13158</x:t>
   </x:si>
   <x:si>
@@ -361,7 +400,10 @@
     <x:t>13</x:t>
   </x:si>
   <x:si>
-    <x:t>FL</x:t>
+    <x:t>S4MI00595</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ROGERS, MICHAEL J</x:t>
   </x:si>
   <x:si>
     <x:t>H6NH01321</x:t>
@@ -386,9 +428,6 @@
   </x:si>
   <x:si>
     <x:t>THOMPSON, MIKE MR.</x:t>
-  </x:si>
-  <x:si>
-    <x:t>CA</x:t>
   </x:si>
   <x:si>
     <x:t>H0WI03175</x:t>
@@ -468,8 +507,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J36" totalsRowShown="0">
-  <x:autoFilter ref="A1:J36"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="Table1" displayName="Table1" ref="A1:J41" totalsRowShown="0">
+  <x:autoFilter ref="A1:J41"/>
   <x:tableColumns count="10">
     <x:tableColumn id="1" name="committee_id" dataDxfId="0"/>
     <x:tableColumn id="2" name="committee_name" dataDxfId="0"/>
@@ -774,7 +813,7 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:J36"/>
+  <x:dimension ref="A1:J41"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="11" max="16384" width="9.140625" style="1" customWidth="1"/>
@@ -1176,10 +1215,10 @@
     </x:row>
     <x:row r="13" spans="1:10">
       <x:c r="A13" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B13" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C13" s="1" t="s">
         <x:v>59</x:v>
@@ -1191,45 +1230,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F13" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="G13" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H13" s="1">
-        <x:v>760499</x:v>
+        <x:v>79599</x:v>
       </x:c>
       <x:c r="I13" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J13" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="14" spans="1:10">
       <x:c r="A14" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B14" s="1" t="s">
+        <x:v>31</x:v>
+      </x:c>
+      <x:c r="C14" s="1" t="s">
         <x:v>63</x:v>
       </x:c>
-      <x:c r="C14" s="1" t="s">
+      <x:c r="D14" s="1" t="s">
         <x:v>64</x:v>
       </x:c>
-      <x:c r="D14" s="1" t="s">
+      <x:c r="E14" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F14" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G14" s="1" t="s">
         <x:v>65</x:v>
       </x:c>
-      <x:c r="E14" s="1" t="s">
-        <x:v>39</x:v>
-      </x:c>
-      <x:c r="F14" s="1" t="s">
-        <x:v>40</x:v>
-      </x:c>
-      <x:c r="G14" s="1" t="s">
-        <x:v>66</x:v>
-      </x:c>
       <x:c r="H14" s="1">
-        <x:v>1331252</x:v>
+        <x:v>760499</x:v>
       </x:c>
       <x:c r="I14" s="1">
         <x:v>2026</x:v>
@@ -1240,16 +1279,16 @@
     </x:row>
     <x:row r="15" spans="1:10">
       <x:c r="A15" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B15" s="1" t="s">
         <x:v>67</x:v>
       </x:c>
-      <x:c r="B15" s="1" t="s">
+      <x:c r="C15" s="1" t="s">
         <x:v>68</x:v>
       </x:c>
-      <x:c r="C15" s="1" t="s">
-        <x:v>64</x:v>
-      </x:c>
       <x:c r="D15" s="1" t="s">
-        <x:v>65</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="E15" s="1" t="s">
         <x:v>39</x:v>
@@ -1258,10 +1297,10 @@
         <x:v>40</x:v>
       </x:c>
       <x:c r="G15" s="1" t="s">
-        <x:v>66</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>587922</x:v>
+        <x:v>1331252</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1272,42 +1311,42 @@
     </x:row>
     <x:row r="16" spans="1:10">
       <x:c r="A16" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B16" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C16" s="1" t="s">
+        <x:v>68</x:v>
+      </x:c>
+      <x:c r="D16" s="1" t="s">
         <x:v>69</x:v>
       </x:c>
-      <x:c r="D16" s="1" t="s">
+      <x:c r="E16" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F16" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G16" s="1" t="s">
         <x:v>70</x:v>
       </x:c>
-      <x:c r="E16" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F16" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
-      <x:c r="G16" s="1" t="s">
-        <x:v>72</x:v>
-      </x:c>
       <x:c r="H16" s="1">
-        <x:v>1999145</x:v>
+        <x:v>689697</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J16" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="17" spans="1:10">
       <x:c r="A17" s="1" t="s">
-        <x:v>24</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B17" s="1" t="s">
-        <x:v>25</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C17" s="1" t="s">
         <x:v>73</x:v>
@@ -1319,13 +1358,13 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F17" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G17" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="H17" s="1">
-        <x:v>4383749</x:v>
+        <x:v>1999145</x:v>
       </x:c>
       <x:c r="I17" s="1">
         <x:v>2026</x:v>
@@ -1336,28 +1375,28 @@
     </x:row>
     <x:row r="18" spans="1:10">
       <x:c r="A18" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="B18" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="C18" s="1" t="s">
-        <x:v>75</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="D18" s="1" t="s">
-        <x:v>76</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="E18" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F18" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G18" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H18" s="1">
-        <x:v>3515616</x:v>
+        <x:v>4383749</x:v>
       </x:c>
       <x:c r="I18" s="1">
         <x:v>2026</x:v>
@@ -1368,28 +1407,28 @@
     </x:row>
     <x:row r="19" spans="1:10">
       <x:c r="A19" s="1" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="B19" s="1" t="s">
+        <x:v>67</x:v>
+      </x:c>
+      <x:c r="C19" s="1" t="s">
         <x:v>79</x:v>
       </x:c>
-      <x:c r="B19" s="1" t="s">
+      <x:c r="D19" s="1" t="s">
         <x:v>80</x:v>
       </x:c>
-      <x:c r="C19" s="1" t="s">
+      <x:c r="E19" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F19" s="1" t="s">
         <x:v>81</x:v>
       </x:c>
-      <x:c r="D19" s="1" t="s">
+      <x:c r="G19" s="1" t="s">
         <x:v>82</x:v>
       </x:c>
-      <x:c r="E19" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F19" s="1" t="s">
-        <x:v>83</x:v>
-      </x:c>
-      <x:c r="G19" s="1" t="s">
-        <x:v>84</x:v>
-      </x:c>
       <x:c r="H19" s="1">
-        <x:v>432350</x:v>
+        <x:v>3515616</x:v>
       </x:c>
       <x:c r="I19" s="1">
         <x:v>2026</x:v>
@@ -1400,10 +1439,10 @@
     </x:row>
     <x:row r="20" spans="1:10">
       <x:c r="A20" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B20" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C20" s="1" t="s">
         <x:v>85</x:v>
@@ -1415,45 +1454,45 @@
         <x:v>14</x:v>
       </x:c>
       <x:c r="F20" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="G20" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="H20" s="1">
-        <x:v>383500</x:v>
+        <x:v>432350</x:v>
       </x:c>
       <x:c r="I20" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J20" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="21" spans="1:10">
       <x:c r="A21" s="1" t="s">
-        <x:v>35</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B21" s="1" t="s">
-        <x:v>36</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C21" s="1" t="s">
-        <x:v>87</x:v>
+        <x:v>89</x:v>
       </x:c>
       <x:c r="D21" s="1" t="s">
-        <x:v>88</x:v>
+        <x:v>90</x:v>
       </x:c>
       <x:c r="E21" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F21" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G21" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H21" s="1">
-        <x:v>83118</x:v>
+        <x:v>383500</x:v>
       </x:c>
       <x:c r="I21" s="1">
         <x:v>2026</x:v>
@@ -1464,60 +1503,60 @@
     </x:row>
     <x:row r="22" spans="1:10">
       <x:c r="A22" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B22" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C22" s="1" t="s">
-        <x:v>89</x:v>
+        <x:v>91</x:v>
       </x:c>
       <x:c r="D22" s="1" t="s">
-        <x:v>90</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="E22" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F22" s="1" t="s">
-        <x:v>71</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="G22" s="1" t="s">
-        <x:v>91</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="H22" s="1">
-        <x:v>900000</x:v>
+        <x:v>48785</x:v>
       </x:c>
       <x:c r="I22" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J22" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="23" spans="1:10">
       <x:c r="A23" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B23" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C23" s="1" t="s">
-        <x:v>92</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D23" s="1" t="s">
-        <x:v>93</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E23" s="1" t="s">
-        <x:v>14</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F23" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>40</x:v>
       </x:c>
       <x:c r="G23" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H23" s="1">
-        <x:v>1433710</x:v>
+        <x:v>83118</x:v>
       </x:c>
       <x:c r="I23" s="1">
         <x:v>2026</x:v>
@@ -1528,28 +1567,28 @@
     </x:row>
     <x:row r="24" spans="1:10">
       <x:c r="A24" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B24" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C24" s="1" t="s">
-        <x:v>95</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="D24" s="1" t="s">
-        <x:v>96</x:v>
+        <x:v>97</x:v>
       </x:c>
       <x:c r="E24" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F24" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G24" s="1" t="s">
-        <x:v>34</x:v>
+        <x:v>98</x:v>
       </x:c>
       <x:c r="H24" s="1">
-        <x:v>278582</x:v>
+        <x:v>203000</x:v>
       </x:c>
       <x:c r="I24" s="1">
         <x:v>2026</x:v>
@@ -1560,28 +1599,28 @@
     </x:row>
     <x:row r="25" spans="1:10">
       <x:c r="A25" s="1" t="s">
-        <x:v>67</x:v>
+        <x:v>42</x:v>
       </x:c>
       <x:c r="B25" s="1" t="s">
-        <x:v>68</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="C25" s="1" t="s">
-        <x:v>98</x:v>
+        <x:v>99</x:v>
       </x:c>
       <x:c r="D25" s="1" t="s">
-        <x:v>99</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="E25" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F25" s="1" t="s">
-        <x:v>97</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G25" s="1" t="s">
-        <x:v>100</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="H25" s="1">
-        <x:v>2326917</x:v>
+        <x:v>900000</x:v>
       </x:c>
       <x:c r="I25" s="1">
         <x:v>2026</x:v>
@@ -1592,28 +1631,28 @@
     </x:row>
     <x:row r="26" spans="1:10">
       <x:c r="A26" s="1" t="s">
-        <x:v>62</x:v>
+        <x:v>83</x:v>
       </x:c>
       <x:c r="B26" s="1" t="s">
-        <x:v>63</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="C26" s="1" t="s">
-        <x:v>101</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D26" s="1" t="s">
-        <x:v>102</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E26" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F26" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="G26" s="1" t="s">
-        <x:v>78</x:v>
+        <x:v>56</x:v>
       </x:c>
       <x:c r="H26" s="1">
-        <x:v>3232621</x:v>
+        <x:v>1899910</x:v>
       </x:c>
       <x:c r="I26" s="1">
         <x:v>2026</x:v>
@@ -1624,28 +1663,28 @@
     </x:row>
     <x:row r="27" spans="1:10">
       <x:c r="A27" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B27" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C27" s="1" t="s">
-        <x:v>103</x:v>
+        <x:v>105</x:v>
       </x:c>
       <x:c r="D27" s="1" t="s">
-        <x:v>104</x:v>
+        <x:v>106</x:v>
       </x:c>
       <x:c r="E27" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F27" s="1" t="s">
-        <x:v>15</x:v>
+        <x:v>107</x:v>
       </x:c>
       <x:c r="G27" s="1" t="s">
-        <x:v>41</x:v>
+        <x:v>34</x:v>
       </x:c>
       <x:c r="H27" s="1">
-        <x:v>347351</x:v>
+        <x:v>278582</x:v>
       </x:c>
       <x:c r="I27" s="1">
         <x:v>2026</x:v>
@@ -1656,60 +1695,60 @@
     </x:row>
     <x:row r="28" spans="1:10">
       <x:c r="A28" s="1" t="s">
-        <x:v>105</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="B28" s="1" t="s">
-        <x:v>106</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="C28" s="1" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="D28" s="1" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="E28" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F28" s="1" t="s">
         <x:v>107</x:v>
       </x:c>
-      <x:c r="D28" s="1" t="s">
-        <x:v>108</x:v>
-      </x:c>
-      <x:c r="E28" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F28" s="1" t="s">
-        <x:v>71</x:v>
-      </x:c>
       <x:c r="G28" s="1" t="s">
-        <x:v>16</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="H28" s="1">
-        <x:v>4379246</x:v>
+        <x:v>2326917</x:v>
       </x:c>
       <x:c r="I28" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J28" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="29" spans="1:10">
       <x:c r="A29" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>66</x:v>
       </x:c>
       <x:c r="B29" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>67</x:v>
       </x:c>
       <x:c r="C29" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="D29" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="E29" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F29" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>81</x:v>
       </x:c>
       <x:c r="G29" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>82</x:v>
       </x:c>
       <x:c r="H29" s="1">
-        <x:v>224344</x:v>
+        <x:v>3232621</x:v>
       </x:c>
       <x:c r="I29" s="1">
         <x:v>2026</x:v>
@@ -1720,28 +1759,28 @@
     </x:row>
     <x:row r="30" spans="1:10">
       <x:c r="A30" s="1" t="s">
-        <x:v>48</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B30" s="1" t="s">
-        <x:v>49</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C30" s="1" t="s">
-        <x:v>109</x:v>
+        <x:v>113</x:v>
       </x:c>
       <x:c r="D30" s="1" t="s">
-        <x:v>110</x:v>
+        <x:v>114</x:v>
       </x:c>
       <x:c r="E30" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F30" s="1" t="s">
-        <x:v>46</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="G30" s="1" t="s">
-        <x:v>111</x:v>
+        <x:v>41</x:v>
       </x:c>
       <x:c r="H30" s="1">
-        <x:v>218493</x:v>
+        <x:v>347351</x:v>
       </x:c>
       <x:c r="I30" s="1">
         <x:v>2026</x:v>
@@ -1752,48 +1791,48 @@
     </x:row>
     <x:row r="31" spans="1:10">
       <x:c r="A31" s="1" t="s">
-        <x:v>30</x:v>
+        <x:v>115</x:v>
       </x:c>
       <x:c r="B31" s="1" t="s">
-        <x:v>31</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="C31" s="1" t="s">
-        <x:v>112</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="D31" s="1" t="s">
-        <x:v>113</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="E31" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F31" s="1" t="s">
-        <x:v>114</x:v>
+        <x:v>75</x:v>
       </x:c>
       <x:c r="G31" s="1" t="s">
-        <x:v>115</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="H31" s="1">
-        <x:v>299290</x:v>
+        <x:v>4379246</x:v>
       </x:c>
       <x:c r="I31" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J31" s="1" t="s">
-        <x:v>17</x:v>
+        <x:v>23</x:v>
       </x:c>
     </x:row>
     <x:row r="32" spans="1:10">
       <x:c r="A32" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B32" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C32" s="1" t="s">
-        <x:v>116</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D32" s="1" t="s">
-        <x:v>117</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E32" s="1" t="s">
         <x:v>14</x:v>
@@ -1802,48 +1841,48 @@
         <x:v>46</x:v>
       </x:c>
       <x:c r="G32" s="1" t="s">
-        <x:v>61</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H32" s="1">
-        <x:v>159276</x:v>
+        <x:v>224344</x:v>
       </x:c>
       <x:c r="I32" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J32" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="33" spans="1:10">
       <x:c r="A33" s="1" t="s">
-        <x:v>42</x:v>
+        <x:v>48</x:v>
       </x:c>
       <x:c r="B33" s="1" t="s">
-        <x:v>43</x:v>
+        <x:v>49</x:v>
       </x:c>
       <x:c r="C33" s="1" t="s">
-        <x:v>118</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="D33" s="1" t="s">
-        <x:v>119</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="E33" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F33" s="1" t="s">
-        <x:v>94</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="G33" s="1" t="s">
-        <x:v>56</x:v>
+        <x:v>121</x:v>
       </x:c>
       <x:c r="H33" s="1">
-        <x:v>19000</x:v>
+        <x:v>218493</x:v>
       </x:c>
       <x:c r="I33" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J33" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="34" spans="1:10">
@@ -1854,22 +1893,22 @@
         <x:v>36</x:v>
       </x:c>
       <x:c r="C34" s="1" t="s">
-        <x:v>120</x:v>
+        <x:v>122</x:v>
       </x:c>
       <x:c r="D34" s="1" t="s">
-        <x:v>121</x:v>
+        <x:v>123</x:v>
       </x:c>
       <x:c r="E34" s="1" t="s">
-        <x:v>39</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="F34" s="1" t="s">
-        <x:v>40</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="G34" s="1" t="s">
-        <x:v>84</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H34" s="1">
-        <x:v>60064</x:v>
+        <x:v>82008</x:v>
       </x:c>
       <x:c r="I34" s="1">
         <x:v>2026</x:v>
@@ -1880,65 +1919,225 @@
     </x:row>
     <x:row r="35" spans="1:10">
       <x:c r="A35" s="1" t="s">
-        <x:v>79</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="B35" s="1" t="s">
-        <x:v>80</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="C35" s="1" t="s">
-        <x:v>122</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="D35" s="1" t="s">
-        <x:v>123</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="E35" s="1" t="s">
         <x:v>14</x:v>
       </x:c>
       <x:c r="F35" s="1" t="s">
-        <x:v>77</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="G35" s="1" t="s">
-        <x:v>124</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="H35" s="1">
-        <x:v>794229</x:v>
+        <x:v>299290</x:v>
       </x:c>
       <x:c r="I35" s="1">
         <x:v>2026</x:v>
       </x:c>
       <x:c r="J35" s="1" t="s">
-        <x:v>23</x:v>
+        <x:v>17</x:v>
       </x:c>
     </x:row>
     <x:row r="36" spans="1:10">
       <x:c r="A36" s="1" t="s">
+        <x:v>71</x:v>
+      </x:c>
+      <x:c r="B36" s="1" t="s">
+        <x:v>72</x:v>
+      </x:c>
+      <x:c r="C36" s="1" t="s">
+        <x:v>128</x:v>
+      </x:c>
+      <x:c r="D36" s="1" t="s">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="E36" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F36" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G36" s="1" t="s">
+        <x:v>70</x:v>
+      </x:c>
+      <x:c r="H36" s="1">
+        <x:v>64393</x:v>
+      </x:c>
+      <x:c r="I36" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J36" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:10">
+      <x:c r="A37" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B37" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C37" s="1" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="D37" s="1" t="s">
+        <x:v>131</x:v>
+      </x:c>
+      <x:c r="E37" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F37" s="1" t="s">
+        <x:v>46</x:v>
+      </x:c>
+      <x:c r="G37" s="1" t="s">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="H37" s="1">
+        <x:v>159276</x:v>
+      </x:c>
+      <x:c r="I37" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J37" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:10">
+      <x:c r="A38" s="1" t="s">
+        <x:v>42</x:v>
+      </x:c>
+      <x:c r="B38" s="1" t="s">
+        <x:v>43</x:v>
+      </x:c>
+      <x:c r="C38" s="1" t="s">
+        <x:v>132</x:v>
+      </x:c>
+      <x:c r="D38" s="1" t="s">
+        <x:v>133</x:v>
+      </x:c>
+      <x:c r="E38" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F38" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G38" s="1" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="H38" s="1">
+        <x:v>19000</x:v>
+      </x:c>
+      <x:c r="I38" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J38" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:10">
+      <x:c r="A39" s="1" t="s">
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="B39" s="1" t="s">
+        <x:v>36</x:v>
+      </x:c>
+      <x:c r="C39" s="1" t="s">
+        <x:v>134</x:v>
+      </x:c>
+      <x:c r="D39" s="1" t="s">
+        <x:v>135</x:v>
+      </x:c>
+      <x:c r="E39" s="1" t="s">
+        <x:v>39</x:v>
+      </x:c>
+      <x:c r="F39" s="1" t="s">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G39" s="1" t="s">
+        <x:v>88</x:v>
+      </x:c>
+      <x:c r="H39" s="1">
+        <x:v>60064</x:v>
+      </x:c>
+      <x:c r="I39" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J39" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:10">
+      <x:c r="A40" s="1" t="s">
+        <x:v>83</x:v>
+      </x:c>
+      <x:c r="B40" s="1" t="s">
+        <x:v>84</x:v>
+      </x:c>
+      <x:c r="C40" s="1" t="s">
+        <x:v>136</x:v>
+      </x:c>
+      <x:c r="D40" s="1" t="s">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="E40" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F40" s="1" t="s">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G40" s="1" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="H40" s="1">
+        <x:v>794229</x:v>
+      </x:c>
+      <x:c r="I40" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J40" s="1" t="s">
+        <x:v>23</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:10">
+      <x:c r="A41" s="1" t="s">
         <x:v>30</x:v>
       </x:c>
-      <x:c r="B36" s="1" t="s">
+      <x:c r="B41" s="1" t="s">
         <x:v>31</x:v>
       </x:c>
-      <x:c r="C36" s="1" t="s">
-        <x:v>125</x:v>
-      </x:c>
-      <x:c r="D36" s="1" t="s">
-        <x:v>126</x:v>
-      </x:c>
-      <x:c r="E36" s="1" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="F36" s="1" t="s">
-        <x:v>94</x:v>
-      </x:c>
-      <x:c r="G36" s="1" t="s">
-        <x:v>127</x:v>
-      </x:c>
-      <x:c r="H36" s="1">
+      <x:c r="C41" s="1" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="D41" s="1" t="s">
+        <x:v>139</x:v>
+      </x:c>
+      <x:c r="E41" s="1" t="s">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="F41" s="1" t="s">
+        <x:v>104</x:v>
+      </x:c>
+      <x:c r="G41" s="1" t="s">
+        <x:v>140</x:v>
+      </x:c>
+      <x:c r="H41" s="1">
         <x:v>299632</x:v>
       </x:c>
-      <x:c r="I36" s="1">
-        <x:v>2026</x:v>
-      </x:c>
-      <x:c r="J36" s="1" t="s">
+      <x:c r="I41" s="1">
+        <x:v>2026</x:v>
+      </x:c>
+      <x:c r="J41" s="1" t="s">
         <x:v>17</x:v>
       </x:c>
     </x:row>

--- a/reports/pro-israel/pro-israel-F24-ie-report.xlsx
+++ b/reports/pro-israel/pro-israel-F24-ie-report.xlsx
@@ -1300,7 +1300,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H15" s="1">
-        <x:v>1331252</x:v>
+        <x:v>1354389</x:v>
       </x:c>
       <x:c r="I15" s="1">
         <x:v>2026</x:v>
@@ -1332,7 +1332,7 @@
         <x:v>70</x:v>
       </x:c>
       <x:c r="H16" s="1">
-        <x:v>689697</x:v>
+        <x:v>763531</x:v>
       </x:c>
       <x:c r="I16" s="1">
         <x:v>2026</x:v>
